--- a/Critical_Part_Type_Register_RevC.xlsx
+++ b/Critical_Part_Type_Register_RevC.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">2. Life limits. If an item is life limited by cycles or operating hours, that alone drives serialization, because remaining life is a per unit quantity. If an item is life limited by shelf life, cure date, or storage age, that drives lot or batch and date code recording instead, because the limit attaches to the manufacturing lot rather than to the individual unit. The same word, life limited, produces opposite record structures depending on which clock is running.</t>
   </si>
   <si>
-    <t xml:space="preserve">3. Cascade scope. A record keeping obligation attaches to the designated item. How far that obligation travels up the product tree is a separate question, set by a different authority. 14 CFR 43.10 and 14 CFR 45.15(c) attach to the part and do not cascade. Quality system traceability under AS9100D 8.5.2 reaches the next higher assembly, and the extent items in that clause sit in a note rather than in the requirement text. DFARS 211.274-2(a)(3)(ii) bounds item unique identification at the parent item that contains the embedded item. Only a contract flowdown reaches the end item. Nothing in this register imposes a cascade. Do not infer one from a designation.</t>
+    <t xml:space="preserve">3. Cascade scope. A record keeping obligation attaches to the designated item. How far that obligation travels up the product tree is a separate question, set by a different authority. 14 CFR 43.10 and 14 CFR 45.15(c) attach to the part and do not cascade. Quality system traceability under AS9100D 8.5.2 reaches the next higher assembly, and the extent items in that clause sit in a note rather than in the requirement text. DFARS 211.274-2(a)(3)(ii) bounds item unique identification at the parent item that contains the embedded item. Nothing in this register imposes a cascade, so do not infer one from a designation. Note that the enterprise directive goes further than any of these: where an item is serialized or lot/batch recorded, serialization and traceability records run to the end item. That directive, not a regulation, is the authority for the end item cascade in the part note code procedure.</t>
   </si>
   <si>
     <t xml:space="preserve">Confidence column</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">C22 Safety-Critical Item: note added recording that MIL-STD-882E states its safety-critical item term is independent of the critical safety item term in Public Laws 108-136 and 109-364.</t>
   </si>
   <si>
-    <t xml:space="preserve">Read Me qualifier 3 added on cascade scope. A record keeping obligation attaches to the designated item; how far it travels up the product tree is set by a different authority and by contract flowdown.</t>
+    <t xml:space="preserve">Read Me qualifier 3 added on cascade scope, recording that a record keeping obligation attaches to the designated item and that the enterprise directive carries serialization and traceability records to the end item. The directive rather than a regulation is the authority for that cascade.</t>
   </si>
   <si>
     <t xml:space="preserve">Recording Rules extended with four drivers carried in the enterprise part note code procedure: casting inspection and casting factor basis, alternative approved material design values, special handling, storage and environmental control, and process and batch conditions.</t>
@@ -2659,7 +2659,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B54"/>
+  <dimension ref="A1:B55"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="118"/>
@@ -2949,6 +2949,9 @@
       <c r="A54" s="4" t="s">
         <v>45</v>
       </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
